--- a/file/table/DAPC_TeoremaPitagoras.xlsx
+++ b/file/table/DAPC_TeoremaPitagoras.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29019"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_SSD2TB\R.DAPC\file\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2498FFED-2BCD-4E13-929C-A7A140CE1EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54145F8C-7EA7-448E-840F-A1B28974FE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="397" windowWidth="14768" windowHeight="10718" xr2:uid="{8AC4CCB8-1BBE-43FF-96F7-B4D3AD3D583F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8AC4CCB8-1BBE-43FF-96F7-B4D3AD3D583F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Pitágoras" sheetId="1" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="DeltaX">Hoja1!$C$6</definedName>
-    <definedName name="DeltaY">Hoja1!$D$6</definedName>
-    <definedName name="L">Hoja1!$C$8</definedName>
+    <definedName name="DeltaX">Pitágoras!$C$7</definedName>
+    <definedName name="DeltaY">Pitágoras!$D$7</definedName>
+    <definedName name="L">Pitágoras!$C$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Nodo</t>
   </si>
@@ -80,13 +81,22 @@
   </si>
   <si>
     <t>Longitud de una línea usando el Teorema de Pitágoras</t>
+  </si>
+  <si>
+    <t>v.20250711</t>
+  </si>
+  <si>
+    <t>Metadata</t>
+  </si>
+  <si>
+    <t>Pass: 1234</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +116,18 @@
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -268,16 +290,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -304,6 +320,18 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -320,6 +348,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>63992</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>135188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1064445</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>163556</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{248B0377-A30E-4236-B538-74A609084D9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="237413" y="135188"/>
+          <a:ext cx="1000453" cy="243830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -639,102 +722,135 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F17F85-04EE-4C00-A616-3BCB8B5C933A}">
-  <dimension ref="B2:D10"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <dimension ref="B1:D11"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="15.86328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="4" width="16.5546875" style="1" customWidth="1"/>
     <col min="5" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D1" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B3" s="8" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C5" s="14">
         <v>690.3</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="15">
         <v>741.15</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C6" s="14">
         <v>3377.07</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D6" s="15">
         <v>742.81</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B6" s="5" t="s">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6">
-        <f>C5-C4</f>
+      <c r="C7" s="4">
+        <f>C6-C5</f>
         <v>2686.7700000000004</v>
       </c>
-      <c r="D6" s="7">
-        <f>D5-D4</f>
+      <c r="D7" s="5">
+        <f>D6-D5</f>
         <v>1.6599999999999682</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B8" s="1" t="s">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C9" s="10">
         <f>(DeltaX^2+DeltaY^2)^0.5</f>
         <v>2686.7705128090124</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D9" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B9" s="1" t="s">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C10" s="10">
         <f>ATAN(DeltaY/DeltaX)</f>
         <v>6.1784216318353131E-4</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D10" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B10" s="1" t="s">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="13">
-        <f>C9*180/PI()</f>
+      <c r="C11" s="11">
+        <f>C10*180/PI()</f>
         <v>3.5399748355649435E-2</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D11" s="9" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="z5TGM82oRuc7FIfwtNXZgxaMIAhJLFRwhQfnsHzT7uCX1uCOy199bws+/j2D8GxM0MpQ3FrR9Lf7XntMwUGNCA==" saltValue="1U2oGYnYWJjR7cPaTohVoQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69752750-9980-4849-99D0-0606AB6E4FDC}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="59.77734375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B3" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="mNsL/W4JiyEetiO9NHx+FYOlw7+LhSeBb33iVL6ZDxfIRKTDkMOmyr/YBaNQwKuSGnXQqy0KFW3m94YoreY7rg==" saltValue="mhr+X6M+gV8xQU60DpuYUg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/file/table/DAPC_TeoremaPitagoras.xlsx
+++ b/file/table/DAPC_TeoremaPitagoras.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29718"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54145F8C-7EA7-448E-840F-A1B28974FE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978939CD-8977-4035-9D09-751B7DD2ED0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8AC4CCB8-1BBE-43FF-96F7-B4D3AD3D583F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8AC4CCB8-1BBE-43FF-96F7-B4D3AD3D583F}"/>
   </bookViews>
   <sheets>
     <sheet name="Pitágoras" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="DeltaX">Pitágoras!$C$7</definedName>
     <definedName name="DeltaY">Pitágoras!$D$7</definedName>
-    <definedName name="L">Pitágoras!$C$9</definedName>
+    <definedName name="L">Pitágoras!$C$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Nodo</t>
   </si>
@@ -83,20 +83,38 @@
     <t>Longitud de una línea usando el Teorema de Pitágoras</t>
   </si>
   <si>
-    <t>v.20250711</t>
-  </si>
-  <si>
     <t>Metadata</t>
   </si>
   <si>
     <t>Pass: 1234</t>
+  </si>
+  <si>
+    <t>Centroide</t>
+  </si>
+  <si>
+    <t>Cálculo de longitud y dirección</t>
+  </si>
+  <si>
+    <t>Parámetro</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Formulación</t>
+  </si>
+  <si>
+    <t>v.20260121</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,12 +129,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="2" tint="-0.249977111117893"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Segoe UI Light"/>
@@ -125,6 +137,17 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="2" tint="-0.249977111117893"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -143,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -286,11 +309,185 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -299,12 +496,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -314,25 +505,60 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -722,108 +948,137 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F17F85-04EE-4C00-A616-3BCB8B5C933A}">
-  <dimension ref="B1:D11"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="B1:D14"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="4" width="16.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.53125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="24" style="1" customWidth="1"/>
     <col min="5" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="D1" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="D1" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="17">
         <v>690.3</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="18">
         <v>741.15</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="19">
         <v>3377.07</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="20">
         <v>742.81</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="21">
         <f>C6-C5</f>
         <v>2686.7700000000004</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="22">
         <f>D6-D5</f>
         <v>1.6599999999999682</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B9" s="1" t="s">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="23">
+        <f>(DeltaX/2)+C5</f>
+        <v>2033.6850000000002</v>
+      </c>
+      <c r="D8" s="24">
+        <f>(DeltaX/2)+D5</f>
+        <v>2084.5350000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" s="10" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="B10" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B11" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B12" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C12" s="25">
         <f>(DeltaX^2+DeltaY^2)^0.5</f>
         <v>2686.7705128090124</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D12" s="27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B10" s="1" t="s">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B13" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C13" s="11">
         <f>ATAN(DeltaY/DeltaX)</f>
         <v>6.1784216318353131E-4</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D13" s="27" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B11" s="1" t="s">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B14" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="11">
-        <f>C10*180/PI()</f>
+      <c r="C14" s="26">
+        <f>C13*180/PI()</f>
         <v>3.5399748355649435E-2</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D14" s="28" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="z5TGM82oRuc7FIfwtNXZgxaMIAhJLFRwhQfnsHzT7uCX1uCOy199bws+/j2D8GxM0MpQ3FrR9Lf7XntMwUGNCA==" saltValue="1U2oGYnYWJjR7cPaTohVoQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -832,21 +1087,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69752750-9980-4849-99D0-0606AB6E4FDC}">
   <dimension ref="B2:B3"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="59.77734375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="2.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="59.796875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.6">
+      <c r="B3" s="8" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="13" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_TeoremaPitagoras.xlsx
+++ b/file/table/DAPC_TeoremaPitagoras.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29718"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978939CD-8977-4035-9D09-751B7DD2ED0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C9C3FF-119B-485E-AF1B-C363790B5FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8AC4CCB8-1BBE-43FF-96F7-B4D3AD3D583F}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{8AC4CCB8-1BBE-43FF-96F7-B4D3AD3D583F}"/>
   </bookViews>
   <sheets>
     <sheet name="Pitágoras" sheetId="1" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="DeltaX">Pitágoras!$C$7</definedName>
-    <definedName name="DeltaY">Pitágoras!$D$7</definedName>
-    <definedName name="L">Pitágoras!$C$12</definedName>
+    <definedName name="DeltaX">Pitágoras!$C$6</definedName>
+    <definedName name="DeltaY">Pitágoras!$D$6</definedName>
+    <definedName name="L">Pitágoras!$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,17 +42,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Nodo</t>
   </si>
   <si>
-    <t>CX</t>
-  </si>
-  <si>
-    <t>CY</t>
-  </si>
-  <si>
     <t>Start</t>
   </si>
   <si>
@@ -62,24 +56,12 @@
     <t>Δ</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Ángulo (°)</t>
-  </si>
-  <si>
-    <t>Ángulo (rad)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> =(DeltaX^2+DeltaY^2)^0.5</t>
   </si>
   <si>
     <t xml:space="preserve"> =ATAN(DeltaY/DeltaX)</t>
   </si>
   <si>
-    <t xml:space="preserve"> =C9*180/PI()</t>
-  </si>
-  <si>
     <t>Longitud de una línea usando el Teorema de Pitágoras</t>
   </si>
   <si>
@@ -105,6 +87,27 @@
   </si>
   <si>
     <t>v.20260121</t>
+  </si>
+  <si>
+    <t>Dirección 2D (rad)</t>
+  </si>
+  <si>
+    <t>Dirección 2D (°)</t>
+  </si>
+  <si>
+    <t>Longitud 2D (m)</t>
+  </si>
+  <si>
+    <t>CX (m)</t>
+  </si>
+  <si>
+    <t>CY (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =ATAN(DeltaY/DeltaX)*180/PI()</t>
+  </si>
+  <si>
+    <t>Dirección asumiendo que el grado decimal cero se encuentra al este.</t>
   </si>
 </sst>
 </file>
@@ -147,7 +150,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="2" tint="-0.249977111117893"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -487,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -512,7 +514,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -559,6 +560,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,16 +587,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>63992</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>701183</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>135188</xdr:rowOff>
+      <xdr:rowOff>151611</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1064445</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1701636</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>163556</xdr:rowOff>
+      <xdr:rowOff>179979</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -618,8 +625,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="237413" y="135188"/>
-          <a:ext cx="1000453" cy="243830"/>
+          <a:off x="3778744" y="151611"/>
+          <a:ext cx="1000453" cy="238575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -959,123 +966,129 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.6">
       <c r="D1" s="7" t="s">
-        <v>20</v>
-      </c>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B2" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="28"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="16">
+        <v>690.3</v>
+      </c>
+      <c r="D4" s="17">
+        <v>741.15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="18">
+        <v>3377.07</v>
+      </c>
+      <c r="D5" s="19">
+        <v>742.81</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="20">
+        <f>C5-C4</f>
+        <v>2686.7700000000004</v>
+      </c>
+      <c r="D6" s="21">
+        <f>D5-D4</f>
+        <v>1.6599999999999682</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="22">
+        <f>(DeltaX/2)+C4</f>
+        <v>2033.6850000000002</v>
+      </c>
+      <c r="D7" s="23">
+        <f>(DeltaY/2)+D4</f>
+        <v>741.98</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="17">
-        <v>690.3</v>
-      </c>
-      <c r="D5" s="18">
-        <v>741.15</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="19">
-        <v>3377.07</v>
-      </c>
-      <c r="D6" s="20">
-        <v>742.81</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="21">
-        <f>C6-C5</f>
-        <v>2686.7700000000004</v>
-      </c>
-      <c r="D7" s="22">
-        <f>D6-D5</f>
-        <v>1.6599999999999682</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="23">
-        <f>(DeltaX/2)+C5</f>
-        <v>2033.6850000000002</v>
-      </c>
-      <c r="D8" s="24">
-        <f>(DeltaX/2)+D5</f>
-        <v>2084.5350000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" s="10" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="B10" s="10" t="s">
-        <v>16</v>
+      <c r="D10" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B12" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="25">
+      <c r="C11" s="24">
         <f>(DeltaX^2+DeltaY^2)^0.5</f>
         <v>2686.7705128090124</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>9</v>
+      <c r="D11" s="26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="10">
+        <f>ATAN(DeltaY/DeltaX)</f>
+        <v>6.1784216318353131E-4</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B13" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="11">
-        <f>ATAN(DeltaY/DeltaX)</f>
-        <v>6.1784216318353131E-4</v>
+        <v>16</v>
+      </c>
+      <c r="C13" s="25">
+        <f>ATAN(DeltaY/DeltaX)*180/PI()</f>
+        <v>3.5399748355649435E-2</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B14" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="26">
-        <f>C13*180/PI()</f>
-        <v>3.5399748355649435E-2</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>11</v>
+      <c r="B14" s="29" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1096,12 +1109,12 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B3" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_TeoremaPitagoras.xlsx
+++ b/file/table/DAPC_TeoremaPitagoras.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C9C3FF-119B-485E-AF1B-C363790B5FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E615D4-D3BF-4CDF-8533-62DB6DE9C4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{8AC4CCB8-1BBE-43FF-96F7-B4D3AD3D583F}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="11333" xr2:uid="{8AC4CCB8-1BBE-43FF-96F7-B4D3AD3D583F}"/>
   </bookViews>
   <sheets>
     <sheet name="Pitágoras" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <t xml:space="preserve"> =ATAN(DeltaY/DeltaX)*180/PI()</t>
   </si>
   <si>
-    <t>Dirección asumiendo que el grado decimal cero se encuentra al este.</t>
+    <t>Dirección con respecto a la horizontal.</t>
   </si>
 </sst>
 </file>
